--- a/backend/data/financials_by_company/1749.HK.xlsx
+++ b/backend/data/financials_by_company/1749.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-954441.925908</v>
+        <v>-1918563.805625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.254279</v>
+        <v>0.110335</v>
       </c>
       <c r="D2" t="n">
-        <v>86435897</v>
+        <v>100920513</v>
       </c>
       <c r="E2" t="n">
-        <v>-3753524</v>
+        <v>-17388561</v>
       </c>
       <c r="F2" t="n">
-        <v>-3753524</v>
+        <v>-17388561</v>
       </c>
       <c r="G2" t="n">
-        <v>33173528</v>
+        <v>21712827</v>
       </c>
       <c r="H2" t="n">
-        <v>32562952</v>
+        <v>54457940</v>
       </c>
       <c r="I2" t="n">
-        <v>627421780</v>
+        <v>507811003</v>
       </c>
       <c r="J2" t="n">
-        <v>82682373</v>
+        <v>83531952</v>
       </c>
       <c r="K2" t="n">
-        <v>50119421</v>
+        <v>29074012</v>
       </c>
       <c r="L2" t="n">
-        <v>-5006038</v>
+        <v>-8179599</v>
       </c>
       <c r="M2" t="n">
-        <v>5634254</v>
+        <v>8868161</v>
       </c>
       <c r="N2" t="n">
-        <v>628216</v>
+        <v>688562</v>
       </c>
       <c r="O2" t="n">
-        <v>35972610.074092</v>
+        <v>37182824.194375</v>
       </c>
       <c r="P2" t="n">
-        <v>33173528</v>
+        <v>12371865</v>
       </c>
       <c r="Q2" t="n">
-        <v>950374570</v>
+        <v>955168853</v>
       </c>
       <c r="R2" t="n">
         <v>133400000</v>
@@ -719,140 +719,144 @@
         <v>133400000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>33173528</v>
+        <v>12371865</v>
       </c>
       <c r="W2" t="n">
-        <v>33173528</v>
+        <v>12371865</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>33173528</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>12371865</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3736385</v>
+      </c>
       <c r="AA2" t="n">
-        <v>33173528</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>8635480</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-9340962</v>
+      </c>
       <c r="AC2" t="n">
-        <v>33173528</v>
+        <v>17976442</v>
       </c>
       <c r="AD2" t="n">
-        <v>11311639</v>
+        <v>2229409</v>
       </c>
       <c r="AE2" t="n">
-        <v>44485167</v>
+        <v>20205851</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3475198</v>
+        <v>-258127</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4108448</v>
+        <v>-6492741</v>
       </c>
       <c r="AH2" t="n">
-        <v>-269991</v>
+        <v>-1798699</v>
       </c>
       <c r="AI2" t="n">
-        <v>1750159</v>
+        <v>6264062</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2628280</v>
+        <v>2027378</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5006038</v>
+        <v>-8179599</v>
       </c>
       <c r="AL2" t="n">
-        <v>5634254</v>
+        <v>8868161</v>
       </c>
       <c r="AM2" t="n">
-        <v>628216</v>
+        <v>688562</v>
       </c>
       <c r="AN2" t="n">
-        <v>56245750</v>
+        <v>37863526</v>
       </c>
       <c r="AO2" t="n">
-        <v>322952790</v>
+        <v>447357850</v>
       </c>
       <c r="AP2" t="n">
-        <v>323761477</v>
+        <v>447742254</v>
       </c>
       <c r="AQ2" t="n">
-        <v>281841736</v>
+        <v>409008150</v>
       </c>
       <c r="AR2" t="n">
-        <v>41919741</v>
+        <v>38734104</v>
       </c>
       <c r="AS2" t="n">
-        <v>379198540</v>
+        <v>485221376</v>
       </c>
       <c r="AT2" t="n">
-        <v>627421780</v>
+        <v>507811003</v>
       </c>
       <c r="AU2" t="n">
-        <v>1006620320</v>
+        <v>993032379</v>
       </c>
       <c r="AV2" t="n">
-        <v>1006620320</v>
+        <v>993032379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-471300.734641</v>
+        <v>736426</v>
       </c>
       <c r="C3" t="n">
-        <v>0.221615</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>87079855</v>
+        <v>67193575</v>
       </c>
       <c r="E3" t="n">
-        <v>-2126667</v>
+        <v>2945704</v>
       </c>
       <c r="F3" t="n">
-        <v>-2126667</v>
+        <v>2945704</v>
       </c>
       <c r="G3" t="n">
-        <v>31605378</v>
+        <v>16006327</v>
       </c>
       <c r="H3" t="n">
-        <v>37800117</v>
+        <v>51390606</v>
       </c>
       <c r="I3" t="n">
-        <v>662806836</v>
+        <v>495306671</v>
       </c>
       <c r="J3" t="n">
-        <v>84953188</v>
+        <v>70139279</v>
       </c>
       <c r="K3" t="n">
-        <v>47153071</v>
+        <v>18748673</v>
       </c>
       <c r="L3" t="n">
-        <v>-5772566</v>
+        <v>-7124629</v>
       </c>
       <c r="M3" t="n">
-        <v>6549299</v>
+        <v>7795763</v>
       </c>
       <c r="N3" t="n">
-        <v>776733</v>
+        <v>671134</v>
       </c>
       <c r="O3" t="n">
-        <v>33260744.265359</v>
+        <v>13797049</v>
       </c>
       <c r="P3" t="n">
-        <v>31605378</v>
+        <v>16006327</v>
       </c>
       <c r="Q3" t="n">
-        <v>1009392135</v>
+        <v>857852979</v>
       </c>
       <c r="R3" t="n">
         <v>133400000</v>
@@ -861,140 +865,144 @@
         <v>133400000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>31605378</v>
+        <v>16006327</v>
       </c>
       <c r="W3" t="n">
-        <v>31605378</v>
+        <v>16006327</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>31605378</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>16006327</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>31605378</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>16006327</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>31605378</v>
+        <v>16006327</v>
       </c>
       <c r="AD3" t="n">
-        <v>8998394</v>
+        <v>-5053417</v>
       </c>
       <c r="AE3" t="n">
-        <v>40603772</v>
+        <v>10952910</v>
       </c>
       <c r="AF3" t="n">
-        <v>580593</v>
+        <v>-2858856</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2103540</v>
+        <v>-1693196</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2706002</v>
+        <v>-2291002</v>
       </c>
       <c r="AI3" t="n">
-        <v>3066537</v>
+        <v>1570303</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1743005</v>
+        <v>2413895</v>
       </c>
       <c r="AK3" t="n">
-        <v>-5772566</v>
+        <v>-7124629</v>
       </c>
       <c r="AL3" t="n">
-        <v>6549299</v>
+        <v>7795763</v>
       </c>
       <c r="AM3" t="n">
-        <v>776733</v>
+        <v>671134</v>
       </c>
       <c r="AN3" t="n">
-        <v>50653839</v>
+        <v>23346682</v>
       </c>
       <c r="AO3" t="n">
-        <v>346585299</v>
+        <v>362546308</v>
       </c>
       <c r="AP3" t="n">
-        <v>348643107</v>
+        <v>363898338</v>
       </c>
       <c r="AQ3" t="n">
-        <v>308249013</v>
+        <v>327077985</v>
       </c>
       <c r="AR3" t="n">
-        <v>40394094</v>
+        <v>36820353</v>
       </c>
       <c r="AS3" t="n">
-        <v>397239138</v>
+        <v>385892990</v>
       </c>
       <c r="AT3" t="n">
-        <v>662806836</v>
+        <v>495306671</v>
       </c>
       <c r="AU3" t="n">
-        <v>1060045974</v>
+        <v>881199661</v>
       </c>
       <c r="AV3" t="n">
-        <v>1060045974</v>
+        <v>881199661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>736426</v>
+        <v>-471300.734641</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.221615</v>
       </c>
       <c r="D4" t="n">
-        <v>67193575</v>
+        <v>87079855</v>
       </c>
       <c r="E4" t="n">
-        <v>2945704</v>
+        <v>-2126667</v>
       </c>
       <c r="F4" t="n">
-        <v>2945704</v>
+        <v>-2126667</v>
       </c>
       <c r="G4" t="n">
-        <v>16006327</v>
+        <v>31605378</v>
       </c>
       <c r="H4" t="n">
-        <v>51390606</v>
+        <v>37800117</v>
       </c>
       <c r="I4" t="n">
-        <v>495306671</v>
+        <v>662806836</v>
       </c>
       <c r="J4" t="n">
-        <v>70139279</v>
+        <v>84953188</v>
       </c>
       <c r="K4" t="n">
-        <v>18748673</v>
+        <v>47153071</v>
       </c>
       <c r="L4" t="n">
-        <v>-7124629</v>
+        <v>-5772566</v>
       </c>
       <c r="M4" t="n">
-        <v>7795763</v>
+        <v>6549299</v>
       </c>
       <c r="N4" t="n">
-        <v>671134</v>
+        <v>776733</v>
       </c>
       <c r="O4" t="n">
-        <v>13797049</v>
+        <v>33260744.265359</v>
       </c>
       <c r="P4" t="n">
-        <v>16006327</v>
+        <v>31605378</v>
       </c>
       <c r="Q4" t="n">
-        <v>857852979</v>
+        <v>1009392135</v>
       </c>
       <c r="R4" t="n">
         <v>133400000</v>
@@ -1003,144 +1011,140 @@
         <v>133400000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="V4" t="n">
-        <v>16006327</v>
+        <v>31605378</v>
       </c>
       <c r="W4" t="n">
-        <v>16006327</v>
+        <v>31605378</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>16006327</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>31605378</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>16006327</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>31605378</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>16006327</v>
+        <v>31605378</v>
       </c>
       <c r="AD4" t="n">
-        <v>-5053417</v>
+        <v>8998394</v>
       </c>
       <c r="AE4" t="n">
-        <v>10952910</v>
+        <v>40603772</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2858856</v>
+        <v>580593</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1693196</v>
+        <v>-2103540</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2291002</v>
+        <v>-2706002</v>
       </c>
       <c r="AI4" t="n">
-        <v>1570303</v>
+        <v>3066537</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2413895</v>
+        <v>1743005</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7124629</v>
+        <v>-5772566</v>
       </c>
       <c r="AL4" t="n">
-        <v>7795763</v>
+        <v>6549299</v>
       </c>
       <c r="AM4" t="n">
-        <v>671134</v>
+        <v>776733</v>
       </c>
       <c r="AN4" t="n">
-        <v>23346682</v>
+        <v>50653839</v>
       </c>
       <c r="AO4" t="n">
-        <v>362546308</v>
+        <v>346585299</v>
       </c>
       <c r="AP4" t="n">
-        <v>363898338</v>
+        <v>348643107</v>
       </c>
       <c r="AQ4" t="n">
-        <v>327077985</v>
+        <v>308249013</v>
       </c>
       <c r="AR4" t="n">
-        <v>36820353</v>
+        <v>40394094</v>
       </c>
       <c r="AS4" t="n">
-        <v>385892990</v>
+        <v>397239138</v>
       </c>
       <c r="AT4" t="n">
-        <v>495306671</v>
+        <v>662806836</v>
       </c>
       <c r="AU4" t="n">
-        <v>881199661</v>
+        <v>1060045974</v>
       </c>
       <c r="AV4" t="n">
-        <v>881199661</v>
+        <v>1060045974</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1918563.805625</v>
+        <v>-954441.925908</v>
       </c>
       <c r="C5" t="n">
-        <v>0.110335</v>
+        <v>0.254279</v>
       </c>
       <c r="D5" t="n">
-        <v>100920513</v>
+        <v>86435897</v>
       </c>
       <c r="E5" t="n">
-        <v>-17388561</v>
+        <v>-3753524</v>
       </c>
       <c r="F5" t="n">
-        <v>-17388561</v>
+        <v>-3753524</v>
       </c>
       <c r="G5" t="n">
-        <v>21712827</v>
+        <v>33173528</v>
       </c>
       <c r="H5" t="n">
-        <v>54457940</v>
+        <v>32562952</v>
       </c>
       <c r="I5" t="n">
-        <v>507811003</v>
+        <v>627421780</v>
       </c>
       <c r="J5" t="n">
-        <v>83531952</v>
+        <v>82682373</v>
       </c>
       <c r="K5" t="n">
-        <v>29074012</v>
+        <v>50119421</v>
       </c>
       <c r="L5" t="n">
-        <v>-8179599</v>
+        <v>-5006038</v>
       </c>
       <c r="M5" t="n">
-        <v>8868161</v>
+        <v>5634254</v>
       </c>
       <c r="N5" t="n">
-        <v>688562</v>
+        <v>628216</v>
       </c>
       <c r="O5" t="n">
-        <v>37182824.194375</v>
+        <v>35972610.074092</v>
       </c>
       <c r="P5" t="n">
-        <v>12371865</v>
+        <v>33173528</v>
       </c>
       <c r="Q5" t="n">
-        <v>955168853</v>
+        <v>950374570</v>
       </c>
       <c r="R5" t="n">
         <v>133400000</v>
@@ -1149,91 +1153,87 @@
         <v>133400000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>12371865</v>
+        <v>33173528</v>
       </c>
       <c r="W5" t="n">
-        <v>12371865</v>
+        <v>33173528</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>12371865</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3736385</v>
-      </c>
+        <v>33173528</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>8635480</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-9340962</v>
-      </c>
+        <v>33173528</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>17976442</v>
+        <v>33173528</v>
       </c>
       <c r="AD5" t="n">
-        <v>2229409</v>
+        <v>11311639</v>
       </c>
       <c r="AE5" t="n">
-        <v>20205851</v>
+        <v>44485167</v>
       </c>
       <c r="AF5" t="n">
-        <v>-258127</v>
+        <v>-3475198</v>
       </c>
       <c r="AG5" t="n">
-        <v>-6492741</v>
+        <v>-4108448</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1798699</v>
+        <v>-269991</v>
       </c>
       <c r="AI5" t="n">
-        <v>6264062</v>
+        <v>1750159</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2027378</v>
+        <v>2628280</v>
       </c>
       <c r="AK5" t="n">
-        <v>-8179599</v>
+        <v>-5006038</v>
       </c>
       <c r="AL5" t="n">
-        <v>8868161</v>
+        <v>5634254</v>
       </c>
       <c r="AM5" t="n">
-        <v>688562</v>
+        <v>628216</v>
       </c>
       <c r="AN5" t="n">
-        <v>37863526</v>
+        <v>56245750</v>
       </c>
       <c r="AO5" t="n">
-        <v>447357850</v>
+        <v>322952790</v>
       </c>
       <c r="AP5" t="n">
-        <v>447742254</v>
+        <v>323761477</v>
       </c>
       <c r="AQ5" t="n">
-        <v>409008150</v>
+        <v>281841736</v>
       </c>
       <c r="AR5" t="n">
-        <v>38734104</v>
+        <v>41919741</v>
       </c>
       <c r="AS5" t="n">
-        <v>485221376</v>
+        <v>379198540</v>
       </c>
       <c r="AT5" t="n">
-        <v>507811003</v>
+        <v>627421780</v>
       </c>
       <c r="AU5" t="n">
-        <v>993032379</v>
+        <v>1006620320</v>
       </c>
       <c r="AV5" t="n">
-        <v>993032379</v>
+        <v>1006620320</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>133400000</v>
@@ -1598,44 +1598,44 @@
         <v>133400000</v>
       </c>
       <c r="D2" t="n">
-        <v>38542925</v>
+        <v>88612220</v>
       </c>
       <c r="E2" t="n">
-        <v>162684433</v>
+        <v>200684888</v>
       </c>
       <c r="F2" t="n">
-        <v>230755025</v>
+        <v>205512208</v>
       </c>
       <c r="G2" t="n">
-        <v>421276449</v>
+        <v>384376762</v>
       </c>
       <c r="H2" t="n">
-        <v>129781707</v>
+        <v>123292748</v>
       </c>
       <c r="I2" t="n">
-        <v>230755025</v>
+        <v>205512208</v>
       </c>
       <c r="J2" t="n">
-        <v>17684433</v>
+        <v>27807342</v>
       </c>
       <c r="K2" t="n">
-        <v>276276449</v>
+        <v>211499216</v>
       </c>
       <c r="L2" t="n">
-        <v>276276449</v>
+        <v>211499216</v>
       </c>
       <c r="M2" t="n">
-        <v>276276449</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>211499216</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>276276449</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10672000</v>
-      </c>
+        <v>211499216</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>88665391</v>
+        <v>35781862</v>
       </c>
       <c r="R2" t="n">
         <v>133400000</v>
@@ -1644,152 +1644,148 @@
         <v>133400000</v>
       </c>
       <c r="T2" t="n">
-        <v>543274312</v>
+        <v>613930310</v>
       </c>
       <c r="U2" t="n">
-        <v>17670144</v>
+        <v>21688594</v>
       </c>
       <c r="V2" t="n">
-        <v>11460000</v>
+        <v>7710000</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>6210144</v>
+        <v>13978594</v>
       </c>
       <c r="Y2" t="n">
-        <v>6210144</v>
+        <v>13978594</v>
       </c>
       <c r="Z2" t="n">
-        <v>525604168</v>
+        <v>592241716</v>
       </c>
       <c r="AA2" t="n">
-        <v>156474289</v>
+        <v>186706294</v>
       </c>
       <c r="AB2" t="n">
-        <v>11474289</v>
+        <v>13828748</v>
       </c>
       <c r="AC2" t="n">
-        <v>145000000</v>
+        <v>172877546</v>
       </c>
       <c r="AD2" t="n">
-        <v>337319556</v>
+        <v>365408963</v>
       </c>
       <c r="AE2" t="n">
-        <v>104263409</v>
+        <v>205012316</v>
       </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>16975742</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>216080405</v>
+        <v>160396647</v>
       </c>
       <c r="AI2" t="n">
-        <v>819550761</v>
+        <v>825429526</v>
       </c>
       <c r="AJ2" t="n">
-        <v>164164886</v>
+        <v>109895062</v>
       </c>
       <c r="AK2" t="n">
-        <v>2007608</v>
+        <v>8166622</v>
       </c>
       <c r="AL2" t="n">
-        <v>20266187</v>
+        <v>19182507</v>
       </c>
       <c r="AM2" t="n">
-        <v>8136142</v>
+        <v>13322965</v>
       </c>
       <c r="AN2" t="n">
-        <v>865214</v>
+        <v>1098601</v>
       </c>
       <c r="AO2" t="n">
-        <v>7270928</v>
+        <v>12224364</v>
       </c>
       <c r="AP2" t="n">
-        <v>45521424</v>
+        <v>5987008</v>
       </c>
       <c r="AQ2" t="n">
-        <v>45521424</v>
+        <v>5987008</v>
       </c>
       <c r="AR2" t="n">
-        <v>86061080</v>
+        <v>63235960</v>
       </c>
       <c r="AS2" t="n">
-        <v>-116865633</v>
+        <v>-85662267</v>
       </c>
       <c r="AT2" t="n">
-        <v>202926713</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>49960159</v>
-      </c>
+        <v>148898227</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>134906</v>
+        <v>648310</v>
       </c>
       <c r="AW2" t="n">
-        <v>132080498</v>
+        <v>119035826</v>
       </c>
       <c r="AX2" t="n">
-        <v>20751150</v>
+        <v>29214091</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>655385875</v>
+        <v>715534464</v>
       </c>
       <c r="BA2" t="n">
-        <v>8500000</v>
+        <v>18856703</v>
       </c>
       <c r="BB2" t="n">
-        <v>21110891</v>
+        <v>46143503</v>
       </c>
       <c r="BC2" t="n">
-        <v>278221780</v>
+        <v>389727583</v>
       </c>
       <c r="BD2" t="n">
-        <v>-74611449</v>
+        <v>-44860890</v>
       </c>
       <c r="BE2" t="n">
-        <v>326831743</v>
+        <v>415844430</v>
       </c>
       <c r="BF2" t="n">
-        <v>14539648</v>
+        <v>10628350</v>
       </c>
       <c r="BG2" t="n">
-        <v>11461838</v>
+        <v>8115693</v>
       </c>
       <c r="BH2" t="n">
-        <v>21835184</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+        <v>520390</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1047487</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>239725926</v>
+        <v>174973472</v>
       </c>
       <c r="BK2" t="n">
-        <v>-29972239</v>
+        <v>-49078566</v>
       </c>
       <c r="BL2" t="n">
-        <v>269698165</v>
+        <v>224052038</v>
       </c>
       <c r="BM2" t="n">
-        <v>107102985</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>645910</v>
-      </c>
+        <v>84265326</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
-        <v>106457075</v>
+        <v>84265326</v>
       </c>
       <c r="BP2" t="n">
-        <v>106457075</v>
+        <v>84265326</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>133400000</v>
@@ -1797,43 +1793,47 @@
       <c r="C3" t="n">
         <v>133400000</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>42811835</v>
+      </c>
       <c r="E3" t="n">
-        <v>145920118</v>
+        <v>172658765</v>
       </c>
       <c r="F3" t="n">
-        <v>207147057</v>
+        <v>219193051</v>
       </c>
       <c r="G3" t="n">
-        <v>388774921</v>
+        <v>385005543</v>
       </c>
       <c r="H3" t="n">
-        <v>172440920</v>
+        <v>170550504</v>
       </c>
       <c r="I3" t="n">
-        <v>207147057</v>
+        <v>219193051</v>
       </c>
       <c r="J3" t="n">
-        <v>10920118</v>
+        <v>15158765</v>
       </c>
       <c r="K3" t="n">
-        <v>253774921</v>
+        <v>227505543</v>
       </c>
       <c r="L3" t="n">
-        <v>253774921</v>
+        <v>227505543</v>
       </c>
       <c r="M3" t="n">
-        <v>253774921</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>227505543</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>253774921</v>
+        <v>227505543</v>
       </c>
       <c r="P3" t="n">
-        <v>10672000</v>
+        <v>5336000</v>
       </c>
       <c r="Q3" t="n">
-        <v>67385567</v>
+        <v>46452189</v>
       </c>
       <c r="R3" t="n">
         <v>133400000</v>
@@ -1842,154 +1842,154 @@
         <v>133400000</v>
       </c>
       <c r="T3" t="n">
-        <v>472614630</v>
+        <v>531071626</v>
       </c>
       <c r="U3" t="n">
-        <v>21703133</v>
+        <v>19877043</v>
       </c>
       <c r="V3" t="n">
-        <v>17346300</v>
+        <v>12069188</v>
       </c>
       <c r="W3" t="n">
-        <v>875986</v>
+        <v>1891524</v>
       </c>
       <c r="X3" t="n">
-        <v>3480847</v>
+        <v>5916331</v>
       </c>
       <c r="Y3" t="n">
-        <v>3480847</v>
+        <v>5916331</v>
       </c>
       <c r="Z3" t="n">
-        <v>450911497</v>
+        <v>511194583</v>
       </c>
       <c r="AA3" t="n">
-        <v>142439271</v>
+        <v>166742434</v>
       </c>
       <c r="AB3" t="n">
-        <v>7439271</v>
+        <v>9242434</v>
       </c>
       <c r="AC3" t="n">
-        <v>135000000</v>
+        <v>157500000</v>
       </c>
       <c r="AD3" t="n">
-        <v>274105164</v>
+        <v>316000153</v>
       </c>
       <c r="AE3" t="n">
-        <v>100430206</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>160674061</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="n">
-        <v>22111537</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>151563421</v>
+        <v>155326092</v>
       </c>
       <c r="AI3" t="n">
-        <v>726389551</v>
+        <v>758577169</v>
       </c>
       <c r="AJ3" t="n">
-        <v>103037134</v>
+        <v>76832082</v>
       </c>
       <c r="AK3" t="n">
-        <v>4639898</v>
+        <v>2655187</v>
       </c>
       <c r="AL3" t="n">
-        <v>19000352</v>
+        <v>23570090</v>
       </c>
       <c r="AM3" t="n">
-        <v>7609058</v>
+        <v>10333657</v>
       </c>
       <c r="AN3" t="n">
-        <v>885920</v>
+        <v>982906</v>
       </c>
       <c r="AO3" t="n">
-        <v>6723138</v>
+        <v>9350751</v>
       </c>
       <c r="AP3" t="n">
-        <v>46627864</v>
+        <v>8312492</v>
       </c>
       <c r="AQ3" t="n">
-        <v>46627864</v>
+        <v>8312492</v>
       </c>
       <c r="AR3" t="n">
-        <v>25159962</v>
+        <v>31960656</v>
       </c>
       <c r="AS3" t="n">
-        <v>-125595633</v>
+        <v>-108376281</v>
       </c>
       <c r="AT3" t="n">
-        <v>150755595</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
+        <v>140336937</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>1400325</v>
+        <v>248006</v>
       </c>
       <c r="AW3" t="n">
-        <v>138052195</v>
+        <v>124634740</v>
       </c>
       <c r="AX3" t="n">
-        <v>11303075</v>
+        <v>15454191</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>623352417</v>
+        <v>681745087</v>
       </c>
       <c r="BA3" t="n">
-        <v>4200305</v>
+        <v>8000050</v>
       </c>
       <c r="BB3" t="n">
-        <v>21558178</v>
+        <v>39088623</v>
       </c>
       <c r="BC3" t="n">
-        <v>230363770</v>
+        <v>311939143</v>
       </c>
       <c r="BD3" t="n">
-        <v>-70820597</v>
+        <v>-63213623</v>
       </c>
       <c r="BE3" t="n">
-        <v>277262414</v>
+        <v>355580163</v>
       </c>
       <c r="BF3" t="n">
-        <v>13301615</v>
+        <v>10429317</v>
       </c>
       <c r="BG3" t="n">
-        <v>10620338</v>
+        <v>9143286</v>
       </c>
       <c r="BH3" t="n">
-        <v>1614109</v>
+        <v>974293</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1713320</v>
       </c>
       <c r="BJ3" t="n">
-        <v>222132260</v>
+        <v>205058626</v>
       </c>
       <c r="BK3" t="n">
-        <v>-34925855</v>
+        <v>-50989260</v>
       </c>
       <c r="BL3" t="n">
-        <v>257058115</v>
+        <v>256047886</v>
       </c>
       <c r="BM3" t="n">
-        <v>143483795</v>
+        <v>114971032</v>
       </c>
       <c r="BN3" t="n">
-        <v>259740</v>
+        <v>282867</v>
       </c>
       <c r="BO3" t="n">
-        <v>143224055</v>
+        <v>114688165</v>
       </c>
       <c r="BP3" t="n">
-        <v>143224055</v>
+        <v>114688165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>133400000</v>
@@ -1997,47 +1997,43 @@
       <c r="C4" t="n">
         <v>133400000</v>
       </c>
-      <c r="D4" t="n">
-        <v>42811835</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>172658765</v>
+        <v>145920118</v>
       </c>
       <c r="F4" t="n">
-        <v>219193051</v>
+        <v>207147057</v>
       </c>
       <c r="G4" t="n">
-        <v>385005543</v>
+        <v>388774921</v>
       </c>
       <c r="H4" t="n">
-        <v>170550504</v>
+        <v>172440920</v>
       </c>
       <c r="I4" t="n">
-        <v>219193051</v>
+        <v>207147057</v>
       </c>
       <c r="J4" t="n">
-        <v>15158765</v>
+        <v>10920118</v>
       </c>
       <c r="K4" t="n">
-        <v>227505543</v>
+        <v>253774921</v>
       </c>
       <c r="L4" t="n">
-        <v>227505543</v>
+        <v>253774921</v>
       </c>
       <c r="M4" t="n">
-        <v>227505543</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>253774921</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>227505543</v>
+        <v>253774921</v>
       </c>
       <c r="P4" t="n">
-        <v>5336000</v>
+        <v>10672000</v>
       </c>
       <c r="Q4" t="n">
-        <v>46452189</v>
+        <v>67385567</v>
       </c>
       <c r="R4" t="n">
         <v>133400000</v>
@@ -2046,154 +2042,154 @@
         <v>133400000</v>
       </c>
       <c r="T4" t="n">
-        <v>531071626</v>
+        <v>472614630</v>
       </c>
       <c r="U4" t="n">
-        <v>19877043</v>
+        <v>21703133</v>
       </c>
       <c r="V4" t="n">
-        <v>12069188</v>
+        <v>17346300</v>
       </c>
       <c r="W4" t="n">
-        <v>1891524</v>
+        <v>875986</v>
       </c>
       <c r="X4" t="n">
-        <v>5916331</v>
+        <v>3480847</v>
       </c>
       <c r="Y4" t="n">
-        <v>5916331</v>
+        <v>3480847</v>
       </c>
       <c r="Z4" t="n">
-        <v>511194583</v>
+        <v>450911497</v>
       </c>
       <c r="AA4" t="n">
-        <v>166742434</v>
+        <v>142439271</v>
       </c>
       <c r="AB4" t="n">
-        <v>9242434</v>
+        <v>7439271</v>
       </c>
       <c r="AC4" t="n">
-        <v>157500000</v>
+        <v>135000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>316000153</v>
+        <v>274105164</v>
       </c>
       <c r="AE4" t="n">
-        <v>160674061</v>
-      </c>
-      <c r="AF4" t="n">
+        <v>100430206</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>22111537</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>151563421</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>726389551</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>103037134</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>4639898</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>19000352</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7609058</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>885920</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>6723138</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>46627864</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>46627864</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>25159962</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-125595633</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>150755595</v>
+      </c>
+      <c r="AU4" t="n">
         <v>0</v>
       </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>155326092</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>758577169</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>76832082</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2655187</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>23570090</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>10333657</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>982906</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>9350751</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8312492</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8312492</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>31960656</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-108376281</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>140336937</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>248006</v>
+        <v>1400325</v>
       </c>
       <c r="AW4" t="n">
-        <v>124634740</v>
+        <v>138052195</v>
       </c>
       <c r="AX4" t="n">
-        <v>15454191</v>
+        <v>11303075</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>681745087</v>
+        <v>623352417</v>
       </c>
       <c r="BA4" t="n">
-        <v>8000050</v>
+        <v>4200305</v>
       </c>
       <c r="BB4" t="n">
-        <v>39088623</v>
+        <v>21558178</v>
       </c>
       <c r="BC4" t="n">
-        <v>311939143</v>
+        <v>230363770</v>
       </c>
       <c r="BD4" t="n">
-        <v>-63213623</v>
+        <v>-70820597</v>
       </c>
       <c r="BE4" t="n">
-        <v>355580163</v>
+        <v>277262414</v>
       </c>
       <c r="BF4" t="n">
-        <v>10429317</v>
+        <v>13301615</v>
       </c>
       <c r="BG4" t="n">
-        <v>9143286</v>
+        <v>10620338</v>
       </c>
       <c r="BH4" t="n">
-        <v>974293</v>
+        <v>1614109</v>
       </c>
       <c r="BI4" t="n">
-        <v>1713320</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>205058626</v>
+        <v>222132260</v>
       </c>
       <c r="BK4" t="n">
-        <v>-50989260</v>
+        <v>-34925855</v>
       </c>
       <c r="BL4" t="n">
-        <v>256047886</v>
+        <v>257058115</v>
       </c>
       <c r="BM4" t="n">
-        <v>114971032</v>
+        <v>143483795</v>
       </c>
       <c r="BN4" t="n">
-        <v>282867</v>
+        <v>259740</v>
       </c>
       <c r="BO4" t="n">
-        <v>114688165</v>
+        <v>143224055</v>
       </c>
       <c r="BP4" t="n">
-        <v>114688165</v>
+        <v>143224055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>133400000</v>
@@ -2202,44 +2198,44 @@
         <v>133400000</v>
       </c>
       <c r="D5" t="n">
-        <v>88612220</v>
+        <v>38542925</v>
       </c>
       <c r="E5" t="n">
-        <v>200684888</v>
+        <v>162684433</v>
       </c>
       <c r="F5" t="n">
-        <v>205512208</v>
+        <v>230755025</v>
       </c>
       <c r="G5" t="n">
-        <v>384376762</v>
+        <v>421276449</v>
       </c>
       <c r="H5" t="n">
-        <v>123292748</v>
+        <v>129781707</v>
       </c>
       <c r="I5" t="n">
-        <v>205512208</v>
+        <v>230755025</v>
       </c>
       <c r="J5" t="n">
-        <v>27807342</v>
+        <v>17684433</v>
       </c>
       <c r="K5" t="n">
-        <v>211499216</v>
+        <v>276276449</v>
       </c>
       <c r="L5" t="n">
-        <v>211499216</v>
+        <v>276276449</v>
       </c>
       <c r="M5" t="n">
-        <v>211499216</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>276276449</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>211499216</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>276276449</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10672000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>35781862</v>
+        <v>88665391</v>
       </c>
       <c r="R5" t="n">
         <v>133400000</v>
@@ -2248,143 +2244,147 @@
         <v>133400000</v>
       </c>
       <c r="T5" t="n">
-        <v>613930310</v>
+        <v>543274312</v>
       </c>
       <c r="U5" t="n">
-        <v>21688594</v>
+        <v>17670144</v>
       </c>
       <c r="V5" t="n">
-        <v>7710000</v>
+        <v>11460000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>13978594</v>
+        <v>6210144</v>
       </c>
       <c r="Y5" t="n">
-        <v>13978594</v>
+        <v>6210144</v>
       </c>
       <c r="Z5" t="n">
-        <v>592241716</v>
+        <v>525604168</v>
       </c>
       <c r="AA5" t="n">
-        <v>186706294</v>
+        <v>156474289</v>
       </c>
       <c r="AB5" t="n">
-        <v>13828748</v>
+        <v>11474289</v>
       </c>
       <c r="AC5" t="n">
-        <v>172877546</v>
+        <v>145000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>365408963</v>
+        <v>337319556</v>
       </c>
       <c r="AE5" t="n">
-        <v>205012316</v>
+        <v>104263409</v>
       </c>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>16975742</v>
+      </c>
       <c r="AH5" t="n">
-        <v>160396647</v>
+        <v>216080405</v>
       </c>
       <c r="AI5" t="n">
-        <v>825429526</v>
+        <v>819550761</v>
       </c>
       <c r="AJ5" t="n">
-        <v>109895062</v>
+        <v>164164886</v>
       </c>
       <c r="AK5" t="n">
-        <v>8166622</v>
+        <v>2007608</v>
       </c>
       <c r="AL5" t="n">
-        <v>19182507</v>
+        <v>20266187</v>
       </c>
       <c r="AM5" t="n">
-        <v>13322965</v>
+        <v>8136142</v>
       </c>
       <c r="AN5" t="n">
-        <v>1098601</v>
+        <v>865214</v>
       </c>
       <c r="AO5" t="n">
-        <v>12224364</v>
+        <v>7270928</v>
       </c>
       <c r="AP5" t="n">
-        <v>5987008</v>
+        <v>45521424</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5987008</v>
+        <v>45521424</v>
       </c>
       <c r="AR5" t="n">
-        <v>63235960</v>
+        <v>86061080</v>
       </c>
       <c r="AS5" t="n">
-        <v>-85662267</v>
+        <v>-116865633</v>
       </c>
       <c r="AT5" t="n">
-        <v>148898227</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>202926713</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>49960159</v>
+      </c>
       <c r="AV5" t="n">
-        <v>648310</v>
+        <v>134906</v>
       </c>
       <c r="AW5" t="n">
-        <v>119035826</v>
+        <v>132080498</v>
       </c>
       <c r="AX5" t="n">
-        <v>29214091</v>
+        <v>20751150</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>715534464</v>
+        <v>655385875</v>
       </c>
       <c r="BA5" t="n">
-        <v>18856703</v>
+        <v>8500000</v>
       </c>
       <c r="BB5" t="n">
-        <v>46143503</v>
+        <v>21110891</v>
       </c>
       <c r="BC5" t="n">
-        <v>389727583</v>
+        <v>278221780</v>
       </c>
       <c r="BD5" t="n">
-        <v>-44860890</v>
+        <v>-74611449</v>
       </c>
       <c r="BE5" t="n">
-        <v>415844430</v>
+        <v>326831743</v>
       </c>
       <c r="BF5" t="n">
-        <v>10628350</v>
+        <v>14539648</v>
       </c>
       <c r="BG5" t="n">
-        <v>8115693</v>
+        <v>11461838</v>
       </c>
       <c r="BH5" t="n">
-        <v>520390</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1047487</v>
-      </c>
+        <v>21835184</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>174973472</v>
+        <v>239725926</v>
       </c>
       <c r="BK5" t="n">
-        <v>-49078566</v>
+        <v>-29972239</v>
       </c>
       <c r="BL5" t="n">
-        <v>224052038</v>
+        <v>269698165</v>
       </c>
       <c r="BM5" t="n">
-        <v>84265326</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>107102985</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>645910</v>
+      </c>
       <c r="BO5" t="n">
-        <v>84265326</v>
+        <v>106457075</v>
       </c>
       <c r="BP5" t="n">
-        <v>84265326</v>
+        <v>106457075</v>
       </c>
     </row>
   </sheetData>
@@ -2640,530 +2640,530 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-8473068</v>
+        <v>24299063</v>
       </c>
       <c r="C2" t="n">
-        <v>-135000000</v>
+        <v>-252561760</v>
       </c>
       <c r="D2" t="n">
-        <v>145000000</v>
+        <v>227006582</v>
       </c>
       <c r="E2" t="n">
-        <v>-46355452</v>
+        <v>-32284894</v>
       </c>
       <c r="F2" t="n">
-        <v>106457075</v>
+        <v>84265326</v>
       </c>
       <c r="G2" t="n">
-        <v>143224055</v>
+        <v>111326251</v>
       </c>
       <c r="H2" t="n">
-        <v>-36766980</v>
+        <v>-27060925</v>
       </c>
       <c r="I2" t="n">
-        <v>-22449988</v>
+        <v>-56653967</v>
       </c>
       <c r="J2" t="n">
-        <v>-5733694</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-10672000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-10672000</v>
-      </c>
+        <v>-8868161</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>10000000</v>
+        <v>-25555178</v>
       </c>
       <c r="N2" t="n">
-        <v>10000000</v>
+        <v>-25555178</v>
       </c>
       <c r="O2" t="n">
-        <v>-135000000</v>
+        <v>-252561760</v>
       </c>
       <c r="P2" t="n">
-        <v>145000000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>227006582</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>227006582</v>
+      </c>
       <c r="T2" t="n">
-        <v>-52199376</v>
+        <v>-26990915</v>
       </c>
       <c r="U2" t="n">
-        <v>-6472140</v>
+        <v>3143297</v>
       </c>
       <c r="V2" t="n">
-        <v>628216</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>688562</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1335503</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1335503</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-46355452</v>
+        <v>-30867271</v>
       </c>
       <c r="AD2" t="n">
+        <v>82120</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-30949391</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>56583957</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="n">
-        <v>-46355452</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>37882384</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-9174954</v>
-      </c>
       <c r="AH2" t="n">
-        <v>-42040033</v>
+        <v>-41800389</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3432725</v>
+        <v>-11603192</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12340575</v>
+        <v>-13945880</v>
       </c>
       <c r="AK2" t="n">
-        <v>2752751</v>
+        <v>-16405299</v>
       </c>
       <c r="AL2" t="n">
-        <v>-51648862</v>
+        <v>18748875</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2051772</v>
+        <v>-18594893</v>
       </c>
       <c r="AN2" t="n">
-        <v>5277123</v>
+        <v>6058821</v>
       </c>
       <c r="AO2" t="n">
-        <v>32562952</v>
+        <v>54457940</v>
       </c>
       <c r="AP2" t="n">
-        <v>1621293</v>
+        <v>741329</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30941659</v>
+        <v>53716611</v>
       </c>
       <c r="AR2" t="n">
-        <v>-354924</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>10895820</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-6092731</v>
+      </c>
       <c r="AT2" t="n">
-        <v>56444</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>1655510</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>44485167</v>
+        <v>10864889</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>77794099</v>
+        <v>64474571</v>
       </c>
       <c r="C3" t="n">
-        <v>-277500000</v>
+        <v>-217218960</v>
       </c>
       <c r="D3" t="n">
-        <v>255000000</v>
+        <v>192500000</v>
       </c>
       <c r="E3" t="n">
-        <v>-56274285</v>
+        <v>-18757688</v>
       </c>
       <c r="F3" t="n">
-        <v>143224055</v>
+        <v>114688165</v>
       </c>
       <c r="G3" t="n">
-        <v>114688165</v>
+        <v>84265326</v>
       </c>
       <c r="H3" t="n">
-        <v>28535890</v>
+        <v>30422839</v>
       </c>
       <c r="I3" t="n">
-        <v>-53927101</v>
+        <v>-49116239</v>
       </c>
       <c r="J3" t="n">
-        <v>-6373976</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-5336000</v>
-      </c>
+        <v>-7795763</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-5336000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-22500000</v>
+        <v>-24718960</v>
       </c>
       <c r="N3" t="n">
-        <v>-22500000</v>
+        <v>-24718960</v>
       </c>
       <c r="O3" t="n">
-        <v>-277500000</v>
+        <v>-217218960</v>
       </c>
       <c r="P3" t="n">
-        <v>255000000</v>
+        <v>192500000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-51605393</v>
+        <v>-3693181</v>
       </c>
       <c r="U3" t="n">
-        <v>3799745</v>
+        <v>10856653</v>
       </c>
       <c r="V3" t="n">
-        <v>776733</v>
+        <v>671134</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2879600</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
+        <v>-220882</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-220882</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-17879686</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>657120</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-18536806</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>83232259</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-56181871</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>92414</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-56274285</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>134068384</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-1170</v>
-      </c>
       <c r="AH3" t="n">
-        <v>35002578</v>
+        <v>-11854827</v>
       </c>
       <c r="AI3" t="n">
-        <v>304053</v>
+        <v>-1220005</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-34736568</v>
+        <v>-38300993</v>
       </c>
       <c r="AK3" t="n">
-        <v>14250679</v>
+        <v>12080018</v>
       </c>
       <c r="AL3" t="n">
-        <v>73968399</v>
+        <v>48787079</v>
       </c>
       <c r="AM3" t="n">
-        <v>-18783985</v>
+        <v>-33200926</v>
       </c>
       <c r="AN3" t="n">
-        <v>6188314</v>
+        <v>6515645</v>
       </c>
       <c r="AO3" t="n">
-        <v>37800117</v>
+        <v>51390606</v>
       </c>
       <c r="AP3" t="n">
-        <v>1803028</v>
+        <v>1795398</v>
       </c>
       <c r="AQ3" t="n">
-        <v>35997089</v>
+        <v>49595208</v>
       </c>
       <c r="AR3" t="n">
-        <v>23127</v>
+        <v>-4638900</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5372904</v>
       </c>
       <c r="AT3" t="n">
-        <v>11478</v>
+        <v>1707810</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>40603772</v>
+        <v>10952910</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>64474571</v>
+        <v>77794099</v>
       </c>
       <c r="C4" t="n">
-        <v>-217218960</v>
+        <v>-277500000</v>
       </c>
       <c r="D4" t="n">
-        <v>192500000</v>
+        <v>255000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-18757688</v>
+        <v>-56274285</v>
       </c>
       <c r="F4" t="n">
+        <v>143224055</v>
+      </c>
+      <c r="G4" t="n">
         <v>114688165</v>
       </c>
-      <c r="G4" t="n">
-        <v>84265326</v>
-      </c>
       <c r="H4" t="n">
-        <v>30422839</v>
+        <v>28535890</v>
       </c>
       <c r="I4" t="n">
-        <v>-49116239</v>
+        <v>-53927101</v>
       </c>
       <c r="J4" t="n">
-        <v>-7795763</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>-6373976</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-5336000</v>
+      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-5336000</v>
       </c>
       <c r="M4" t="n">
-        <v>-24718960</v>
+        <v>-22500000</v>
       </c>
       <c r="N4" t="n">
-        <v>-24718960</v>
+        <v>-22500000</v>
       </c>
       <c r="O4" t="n">
-        <v>-217218960</v>
+        <v>-277500000</v>
       </c>
       <c r="P4" t="n">
-        <v>192500000</v>
+        <v>255000000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-3693181</v>
+        <v>-51605393</v>
       </c>
       <c r="U4" t="n">
-        <v>10856653</v>
+        <v>3799745</v>
       </c>
       <c r="V4" t="n">
-        <v>671134</v>
+        <v>776733</v>
       </c>
       <c r="W4" t="n">
-        <v>2879600</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-220882</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-220882</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-17879686</v>
+        <v>-56181871</v>
       </c>
       <c r="AD4" t="n">
-        <v>657120</v>
+        <v>92414</v>
       </c>
       <c r="AE4" t="n">
-        <v>-18536806</v>
+        <v>-56274285</v>
       </c>
       <c r="AF4" t="n">
-        <v>83232259</v>
+        <v>134068384</v>
       </c>
       <c r="AG4" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>35002578</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>304053</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-34736568</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>14250679</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>73968399</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-18783985</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6188314</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>37800117</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1803028</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>35997089</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>23127</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="n">
-        <v>-11854827</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1220005</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-38300993</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>12080018</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>48787079</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-33200926</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6515645</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>51390606</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1795398</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>49595208</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-4638900</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5372904</v>
-      </c>
       <c r="AT4" t="n">
-        <v>1707810</v>
+        <v>11478</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>10952910</v>
+        <v>40603772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>24299063</v>
+        <v>-8473068</v>
       </c>
       <c r="C5" t="n">
-        <v>-252561760</v>
+        <v>-135000000</v>
       </c>
       <c r="D5" t="n">
-        <v>227006582</v>
+        <v>145000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-32284894</v>
+        <v>-46355452</v>
       </c>
       <c r="F5" t="n">
-        <v>84265326</v>
+        <v>106457075</v>
       </c>
       <c r="G5" t="n">
-        <v>111326251</v>
+        <v>143224055</v>
       </c>
       <c r="H5" t="n">
-        <v>-27060925</v>
+        <v>-36766980</v>
       </c>
       <c r="I5" t="n">
-        <v>-56653967</v>
+        <v>-22449988</v>
       </c>
       <c r="J5" t="n">
-        <v>-8868161</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>-5733694</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-10672000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-10672000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-25555178</v>
+        <v>10000000</v>
       </c>
       <c r="N5" t="n">
-        <v>-25555178</v>
+        <v>10000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-252561760</v>
+        <v>-135000000</v>
       </c>
       <c r="P5" t="n">
-        <v>227006582</v>
-      </c>
-      <c r="Q5" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>-52199376</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-6472140</v>
+      </c>
+      <c r="V5" t="n">
+        <v>628216</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>-46355452</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>227006582</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-26990915</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3143297</v>
-      </c>
-      <c r="V5" t="n">
-        <v>688562</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1380000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1335503</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1335503</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-30867271</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>82120</v>
-      </c>
       <c r="AE5" t="n">
-        <v>-30949391</v>
+        <v>-46355452</v>
       </c>
       <c r="AF5" t="n">
-        <v>56583957</v>
+        <v>37882384</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-9174954</v>
       </c>
       <c r="AH5" t="n">
-        <v>-41800389</v>
+        <v>-42040033</v>
       </c>
       <c r="AI5" t="n">
-        <v>-11603192</v>
+        <v>-3432725</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-13945880</v>
+        <v>12340575</v>
       </c>
       <c r="AK5" t="n">
-        <v>-16405299</v>
+        <v>2752751</v>
       </c>
       <c r="AL5" t="n">
-        <v>18748875</v>
+        <v>-51648862</v>
       </c>
       <c r="AM5" t="n">
-        <v>-18594893</v>
+        <v>-2051772</v>
       </c>
       <c r="AN5" t="n">
-        <v>6058821</v>
+        <v>5277123</v>
       </c>
       <c r="AO5" t="n">
-        <v>54457940</v>
+        <v>32562952</v>
       </c>
       <c r="AP5" t="n">
-        <v>741329</v>
+        <v>1621293</v>
       </c>
       <c r="AQ5" t="n">
-        <v>53716611</v>
+        <v>30941659</v>
       </c>
       <c r="AR5" t="n">
-        <v>10895820</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-6092731</v>
-      </c>
+        <v>-354924</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1655510</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>56444</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>10864889</v>
+        <v>44485167</v>
       </c>
     </row>
   </sheetData>
@@ -3693,187 +3693,187 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yefei  Luo', 'age': 50, 'title': 'GM &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 800819, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Cao', 'age': 53, 'title': 'Executive Vice Chairman', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 63442, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jingfen  Yan', 'age': 51, 'title': 'VP, CFO, Joint Company Secretary &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 638373, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yumei  Zhou', 'age': 55, 'title': 'GM of Asset Management Department &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 349446, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong  Yang', 'age': 56, 'title': 'Deputy GM, Head of Design and GM of Product Research &amp; Developm ent Center', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lucy  Cheng FCS', 'title': 'Joint Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yefei  Luo', 'age': 50, 'title': 'GM &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 800181, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Cao', 'age': 53, 'title': 'Executive Vice Chairman', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 63391, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jingfen  Yan', 'age': 51, 'title': 'VP, CFO, Joint Company Secretary &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 637864, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yumei  Zhou', 'age': 55, 'title': 'GM of Asset Management Department &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 349168, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong  Yang', 'age': 56, 'title': 'Deputy GM, Head of Design and GM of Product Research &amp; Developm ent Center', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lucy  Cheng FCS', 'title': 'Joint Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3971,34 +3971,34 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="U2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="W2" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="X2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="AB2" t="n">
         <v>0.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.05</v>
+        <v>16.17</v>
       </c>
       <c r="AD2" t="n">
         <v>1749686400</v>
@@ -4007,31 +4007,31 @@
         <v>1.3296001</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.057</v>
+        <v>1.051</v>
       </c>
       <c r="AG2" t="n">
-        <v>8.285714</v>
+        <v>7.285714</v>
       </c>
       <c r="AH2" t="n">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="AI2" t="n">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>103250</v>
+        <v>61423</v>
       </c>
       <c r="AK2" t="n">
-        <v>45700</v>
+        <v>35300</v>
       </c>
       <c r="AL2" t="n">
-        <v>45700</v>
+        <v>35300</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>77372000</v>
+        <v>68034000</v>
       </c>
       <c r="AR2" t="n">
-        <v>77372000</v>
+        <v>68034000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AU2" t="n">
         <v>4.83</v>
@@ -4058,13 +4058,13 @@
         <v>0.35</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08967538</v>
+        <v>0.07885249</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5848</v>
+        <v>0.5708</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7624</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>211709200</v>
+        <v>202371200</v>
       </c>
       <c r="BE2" t="n">
         <v>0.00915</v>
@@ -4096,10 +4096,10 @@
         <v>133400000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.3748047</v>
+        <v>2.3729308</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.2442306</v>
+        <v>0.2149241</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4117,16 +4117,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.245</v>
+        <v>0.235</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.868</v>
+        <v>6.566</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.46296299</v>
+        <v>-0.5188679</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.0873</v>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4241,63 +4241,61 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="CZ2" t="b">
+          <t>SHANSHAN</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Shanshan Brand Management Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DC2" t="b">
         <v>0</v>
       </c>
-      <c r="DA2" t="n">
-        <v>1530063000000</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.00999999</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>0.58 - 0.58</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>0.47 - 0.51</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.06999999</v>
-      </c>
       <c r="DG2" t="n">
-        <v>0.1372549</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>0.51 - 1.23</t>
-        </is>
+        <v>61423</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.03999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.65000004</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.5284553</v>
+        <v>0.085106365</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.47 - 1.13</t>
+        </is>
       </c>
       <c r="DK2" t="n">
-        <v>-46.2963</v>
+        <v>-0.62</v>
       </c>
       <c r="DL2" t="n">
+        <v>-0.54867256</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-51.88679</v>
+      </c>
+      <c r="DN2" t="n">
         <v>1742906029</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>SHANSHAN</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Shanshan Brand Management Co., Ltd.</t>
-        </is>
       </c>
       <c r="DO2" t="n">
         <v>1742906029</v>
@@ -4309,70 +4307,72 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.0048000216</v>
+        <v>-0.060800016</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.008207971</v>
+        <v>-0.106517196</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0.20380002</v>
+        <v>-0.25239998</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0.26001534</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
+        <v>-0.3310598</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX2" t="b">
+        <v>1782115148</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>finmb_570011087</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="ED2" t="b">
         <v>0</v>
       </c>
-      <c r="DY2" t="n">
-        <v>-1.6949137</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>1780291234</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>finmb_570011087</t>
-        </is>
-      </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EI2" t="b">
+        <v>1530063000000</v>
+      </c>
+      <c r="EH2" t="n">
         <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.51</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
